--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GA3\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GA3\Desktop\Unitydesu\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="ゲームの大まかな動き" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="ボス" sheetId="5" r:id="rId4"/>
     <sheet name="ステージ" sheetId="4" r:id="rId5"/>
     <sheet name="SHOP" sheetId="6" r:id="rId6"/>
+    <sheet name="ステータス一覧" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="82">
   <si>
     <t>ゲームの動き</t>
     <rPh sb="4" eb="5">
@@ -863,6 +864,92 @@
     </rPh>
     <rPh sb="11" eb="12">
       <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃力</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>防御</t>
+    <rPh sb="0" eb="2">
+      <t>ボウギョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>５０スタート</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>２０スタート</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>１００か２００</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最大１０スタート</t>
+    <rPh sb="0" eb="2">
+      <t>サイダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>１０スタート</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>２０か３０</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SHOPで購入</t>
+    <rPh sb="5" eb="7">
+      <t>コウニュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（防御は受けるダメージを１０カットする）</t>
+    <rPh sb="1" eb="3">
+      <t>ボウギョ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（１０回攻撃を防いだら壊れる）</t>
+    <rPh sb="3" eb="4">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>フセ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>コワ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -896,12 +983,147 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -910,12 +1132,42 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1971,4 +2223,82 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B3:E9"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="3" max="3" width="15.5" customWidth="1"/>
+    <col min="4" max="4" width="17.125" customWidth="1"/>
+    <col min="5" max="5" width="18.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:5" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B4" s="3"/>
+      <c r="C4" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B5" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B6" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B7" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D7" s="5"/>
+      <c r="E7" s="6"/>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="C8" s="11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="C9" s="11" t="s">
+        <v>81</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -9,16 +9,17 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" activeTab="6"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="ゲームの大まかな動き" sheetId="1" r:id="rId1"/>
     <sheet name="プレイヤー" sheetId="2" r:id="rId2"/>
     <sheet name="敵" sheetId="3" r:id="rId3"/>
     <sheet name="ボス" sheetId="5" r:id="rId4"/>
-    <sheet name="ステージ" sheetId="4" r:id="rId5"/>
-    <sheet name="SHOP" sheetId="6" r:id="rId6"/>
-    <sheet name="ステータス一覧" sheetId="7" r:id="rId7"/>
+    <sheet name="SHOP" sheetId="6" r:id="rId5"/>
+    <sheet name="ステータス一覧" sheetId="7" r:id="rId6"/>
+    <sheet name="ステージ" sheetId="4" r:id="rId7"/>
+    <sheet name="Stage1" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="86">
   <si>
     <t>ゲームの動き</t>
     <rPh sb="4" eb="5">
@@ -951,6 +952,34 @@
     <rPh sb="11" eb="12">
       <t>コワ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>壊れる壁</t>
+    <rPh sb="0" eb="1">
+      <t>コワ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>カベ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>壁</t>
+    <rPh sb="0" eb="1">
+      <t>カベ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>動くステージ</t>
+    <rPh sb="0" eb="1">
+      <t>ウゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゴール</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1476,6 +1505,1600 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>371475</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>219075</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="正方形/長方形 12"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7572375" y="1685925"/>
+          <a:ext cx="6515100" cy="2343150"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>314325</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="正方形/長方形 4"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7172325" y="514350"/>
+          <a:ext cx="2038350" cy="4476750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="正方形/長方形 1"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="571500" y="514350"/>
+          <a:ext cx="6515100" cy="2343150"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>361950</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="正方形/長方形 2"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5162550" y="514350"/>
+          <a:ext cx="2038350" cy="4476750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="正方形/長方形 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7077075" y="2647950"/>
+          <a:ext cx="257175" cy="2343150"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="7030A0"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>219075</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="正方形/長方形 5"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7077075" y="495300"/>
+          <a:ext cx="257175" cy="2343150"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>561975</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>157165</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>371475</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>176215</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="正方形/長方形 6"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="2738437" y="600078"/>
+          <a:ext cx="257175" cy="4610100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>561974</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>147642</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>371477</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>166692</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="正方形/長方形 7"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="4795838" y="-3848097"/>
+          <a:ext cx="257175" cy="8724903"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>252412</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>152403</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>509587</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="正方形/長方形 9"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5053012" y="2771778"/>
+          <a:ext cx="257175" cy="2266947"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>66677</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>138117</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>561977</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>157167</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="正方形/長方形 10"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="7043739" y="2724155"/>
+          <a:ext cx="257175" cy="4610100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="正方形/長方形 11"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="438150" y="600075"/>
+          <a:ext cx="257175" cy="2343150"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>100018</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>485775</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>119068</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="正方形/長方形 13"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="11558587" y="1524006"/>
+          <a:ext cx="257175" cy="5029200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>61919</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>447675</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>80969</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="正方形/長方形 14"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="11520487" y="-895343"/>
+          <a:ext cx="257175" cy="5029200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>552450</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="正方形/長方形 15"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14011275" y="1724025"/>
+          <a:ext cx="257175" cy="2343150"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>42869</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>61919</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="正方形/長方形 16"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="1014412" y="5915032"/>
+          <a:ext cx="257175" cy="895350"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>14288</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>42863</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>428625</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>61913</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="正方形/長方形 17"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="2493169" y="5812632"/>
+          <a:ext cx="257175" cy="1100137"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="7030A0"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>57149</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>190499</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="正方形/長方形 18"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3457575" y="6248399"/>
+          <a:ext cx="1600200" cy="847725"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>638175</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="楕円 19"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="704850" y="5086350"/>
+          <a:ext cx="619125" cy="571500"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>657225</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="楕円 20"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2095500" y="5095875"/>
+          <a:ext cx="619125" cy="571500"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>657225</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="楕円 21"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3467100" y="5086350"/>
+          <a:ext cx="619125" cy="571500"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>219075</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name="楕円 22"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="990600" y="1409700"/>
+          <a:ext cx="619125" cy="571500"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="楕円 23"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3886200" y="771525"/>
+          <a:ext cx="619125" cy="571500"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>628650</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="25" name="楕円 24"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6181725" y="1828800"/>
+          <a:ext cx="619125" cy="571500"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>409575</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="26" name="楕円 25"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7953375" y="1104900"/>
+          <a:ext cx="619125" cy="571500"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>428625</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="27" name="楕円 26"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8039100" y="4143375"/>
+          <a:ext cx="619125" cy="571500"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>371475</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="28" name="楕円 27"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10725150" y="1847850"/>
+          <a:ext cx="619125" cy="571500"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="29" name="楕円 28"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13058775" y="2476500"/>
+          <a:ext cx="619125" cy="571500"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
@@ -2131,71 +3754,6 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A18"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="1" width="47.875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A3" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A16" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A17" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A18" t="s">
-        <v>30</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -2225,7 +3783,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B3:E9"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
@@ -2301,4 +3859,103 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A18"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="47.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A3" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A16" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B21:F26"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" t="s">
+        <v>85</v>
+      </c>
+      <c r="F21" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B26" t="s">
+        <v>83</v>
+      </c>
+      <c r="D26" t="s">
+        <v>82</v>
+      </c>
+      <c r="F26" t="s">
+        <v>84</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="88">
   <si>
     <t>ゲームの動き</t>
     <rPh sb="4" eb="5">
@@ -980,6 +980,20 @@
   </si>
   <si>
     <t>ゴール</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スイッチ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>消える壁</t>
+    <rPh sb="0" eb="1">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>カベ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1509,16 +1523,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>259897</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>114299</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>371475</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>219075</xdr:rowOff>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>602797</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>69396</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1527,8 +1541,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7572375" y="1685925"/>
-          <a:ext cx="6515100" cy="2343150"/>
+          <a:off x="18629540" y="2563585"/>
+          <a:ext cx="6466114" cy="2404382"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1566,16 +1580,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>314325</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>327932</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>78921</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>295275</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>228600</xdr:rowOff>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>308883</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>24492</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1584,8 +1598,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7172325" y="514350"/>
-          <a:ext cx="2038350" cy="4476750"/>
+          <a:off x="18017218" y="1793421"/>
+          <a:ext cx="2022022" cy="4599214"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1623,16 +1637,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>571500</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>108857</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>187779</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>612321</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>149680</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1641,8 +1655,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="571500" y="514350"/>
-          <a:ext cx="6515100" cy="2343150"/>
+          <a:off x="1469571" y="922565"/>
+          <a:ext cx="3224893" cy="2411186"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1680,16 +1694,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>361950</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>484415</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>78921</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>342900</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>228600</xdr:rowOff>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>465364</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>24492</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1698,8 +1712,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5162550" y="514350"/>
-          <a:ext cx="2038350" cy="4476750"/>
+          <a:off x="16132629" y="1793421"/>
+          <a:ext cx="2022021" cy="4599214"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1737,16 +1751,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>219075</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>273503</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>69396</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>476250</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>228600</xdr:rowOff>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>530678</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>24492</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1755,8 +1769,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7077075" y="2647950"/>
-          <a:ext cx="257175" cy="2343150"/>
+          <a:off x="17962789" y="3988253"/>
+          <a:ext cx="257175" cy="2404382"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1794,26 +1808,26 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>219075</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>524555</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>152402</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>476250</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>219075</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>101373</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="正方形/長方形 5"/>
+        <xdr:cNvPr id="10" name="正方形/長方形 9"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7077075" y="495300"/>
-          <a:ext cx="257175" cy="2343150"/>
+          <a:off x="4606698" y="887188"/>
+          <a:ext cx="257175" cy="2334983"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1856,26 +1870,26 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>561975</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>157165</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>39463</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>83689</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>371475</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>176215</xdr:rowOff>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>534763</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>102739</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="正方形/長方形 6"/>
+        <xdr:cNvPr id="11" name="正方形/長方形 10"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm rot="5400000">
-          <a:off x="2738437" y="600078"/>
-          <a:ext cx="257175" cy="4610100"/>
+          <a:off x="17844409" y="4050171"/>
+          <a:ext cx="263979" cy="4577443"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1918,26 +1932,26 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>561974</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>147642</xdr:rowOff>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>502106</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>113625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>371477</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>166692</xdr:rowOff>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>50349</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>132676</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="正方形/長方形 7"/>
+        <xdr:cNvPr id="14" name="正方形/長方形 13"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm rot="5400000">
-          <a:off x="4795838" y="-3848097"/>
-          <a:ext cx="257175" cy="8724903"/>
+          <a:off x="22596023" y="2403708"/>
+          <a:ext cx="263979" cy="4991100"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1980,26 +1994,26 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>252412</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>152403</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>81642</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>163287</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>509587</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>653145</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>217044</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="正方形/長方形 9"/>
+        <xdr:cNvPr id="15" name="正方形/長方形 14"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5053012" y="2771778"/>
-          <a:ext cx="257175" cy="2266947"/>
+        <a:xfrm rot="5400000">
+          <a:off x="2939479" y="-843979"/>
+          <a:ext cx="298686" cy="3292932"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2042,264 +2056,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>66677</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>138117</xdr:rowOff>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>567418</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>97972</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>561977</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>157167</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="正方形/長方形 10"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="5400000">
-          <a:off x="7043739" y="2724155"/>
-          <a:ext cx="257175" cy="4610100"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="tx1"/>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>438150</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="12" name="正方形/長方形 11"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="438150" y="600075"/>
-          <a:ext cx="257175" cy="2343150"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="tx1"/>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>257175</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>100018</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>485775</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>119068</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="14" name="正方形/長方形 13"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="5400000">
-          <a:off x="11558587" y="1524006"/>
-          <a:ext cx="257175" cy="5029200"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="tx1"/>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>219075</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>61919</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>447675</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>80969</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="15" name="正方形/長方形 14"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="5400000">
-          <a:off x="11520487" y="-895343"/>
-          <a:ext cx="257175" cy="5029200"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="tx1"/>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>295275</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>552450</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>144236</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>59873</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2308,8 +2074,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14011275" y="1724025"/>
-          <a:ext cx="257175" cy="2343150"/>
+          <a:off x="25060275" y="2547258"/>
+          <a:ext cx="257175" cy="2411186"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2699,16 +2465,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>219075</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>372836</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>306161</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>130629</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2717,8 +2483,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="990600" y="1409700"/>
-          <a:ext cx="619125" cy="571500"/>
+          <a:off x="1733550" y="1743075"/>
+          <a:ext cx="613682" cy="591911"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
@@ -2757,15 +2523,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:colOff>348343</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>111578</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>390525</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:colOff>281668</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>206828</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2774,14 +2540,366 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3886200" y="771525"/>
-          <a:ext cx="619125" cy="571500"/>
+          <a:off x="3750129" y="1336221"/>
+          <a:ext cx="613682" cy="585107"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
           <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>70756</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>138794</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>642259</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>192552</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="30" name="正方形/長方形 29"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="2928593" y="1580814"/>
+          <a:ext cx="298686" cy="3292932"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>595313</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>127909</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>172131</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>13607</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="31" name="正方形/長方形 30"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1275670" y="862695"/>
+          <a:ext cx="257175" cy="2334983"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>40822</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>61232</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>659947</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>156482</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="32" name="楕円 31"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4803322" y="5204732"/>
+          <a:ext cx="619125" cy="585107"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent6"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>410936</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>349704</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>50346</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="33" name="楕円 32"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3812722" y="2404382"/>
+          <a:ext cx="619125" cy="585107"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent6"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>108856</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>13607</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>108856</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="34" name="正方形/長方形 33"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5595257" y="843642"/>
+          <a:ext cx="3943350" cy="3184071"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>280307</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>213632</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="35" name="楕円 34"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5723164" y="1650546"/>
+          <a:ext cx="613682" cy="591911"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5"/>
         </a:solidFill>
       </xdr:spPr>
       <xdr:style>
@@ -2814,25 +2932,25 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
+      <xdr:colOff>595994</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>87085</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>628650</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>529319</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>182335</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="25" name="楕円 24"/>
+        <xdr:cNvPr id="36" name="楕円 35"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6181725" y="1828800"/>
-          <a:ext cx="619125" cy="571500"/>
+          <a:off x="6719208" y="1066799"/>
+          <a:ext cx="613682" cy="585107"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
@@ -2870,26 +2988,26 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>409575</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>517072</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>35378</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>342900</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>450397</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>130627</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="26" name="楕円 25"/>
+        <xdr:cNvPr id="37" name="楕円 36"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7953375" y="1104900"/>
-          <a:ext cx="619125" cy="571500"/>
+          <a:off x="8681358" y="3219449"/>
+          <a:ext cx="613682" cy="585107"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
@@ -2927,32 +3045,32 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>495300</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>291193</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>93890</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>428625</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>229961</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>189139</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="27" name="楕円 26"/>
+        <xdr:cNvPr id="38" name="楕円 37"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8039100" y="4143375"/>
-          <a:ext cx="619125" cy="571500"/>
+          <a:off x="5734050" y="3277961"/>
+          <a:ext cx="619125" cy="585107"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:srgbClr val="FF0000"/>
+          <a:schemeClr val="accent6"/>
         </a:solidFill>
       </xdr:spPr>
       <xdr:style>
@@ -2984,32 +3102,32 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>438150</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>98655</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>165329</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>371475</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>512993</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>184378</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="28" name="楕円 27"/>
+        <xdr:cNvPr id="41" name="正方形/長方形 40"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10725150" y="1847850"/>
-          <a:ext cx="619125" cy="571500"/>
+        <a:xfrm rot="5400000">
+          <a:off x="5956871" y="2444184"/>
+          <a:ext cx="263978" cy="1094695"/>
         </a:xfrm>
-        <a:prstGeom prst="ellipse">
+        <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:srgbClr val="FF0000"/>
+          <a:srgbClr val="7030A0"/>
         </a:solidFill>
       </xdr:spPr>
       <xdr:style>
@@ -3041,32 +3159,689 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>513670</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>54429</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>647700</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>68037</xdr:colOff>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="29" name="楕円 28"/>
+        <xdr:cNvPr id="42" name="正方形/長方形 41"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13058775" y="2476500"/>
-          <a:ext cx="619125" cy="571500"/>
+          <a:off x="6636884" y="2993572"/>
+          <a:ext cx="234724" cy="1115785"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>87084</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>13607</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>81643</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>113630</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="43" name="正方形/長方形 42"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="7395816" y="2066589"/>
+          <a:ext cx="344952" cy="4076702"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>622526</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>68036</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>272143</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>149679</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="44" name="正方形/長方形 43"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9467169" y="802822"/>
+          <a:ext cx="329974" cy="3265714"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>584426</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>57151</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>234043</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>138794</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="45" name="正方形/長方形 44"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5346926" y="791937"/>
+          <a:ext cx="329974" cy="3265714"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>103412</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>111579</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>97971</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>211602</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="46" name="正方形/長方形 45"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="7412144" y="-1264439"/>
+          <a:ext cx="344952" cy="4076702"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>71438</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>206148</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>312964</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>81646</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="47" name="正方形/長方形 46"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="3043917" y="2594884"/>
+          <a:ext cx="1100140" cy="241526"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="7030A0"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>244927</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>108860</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>578305</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>170776</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="48" name="正方形/長方形 47"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="4000159" y="1714843"/>
+          <a:ext cx="306844" cy="1013735"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>30616</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>15651</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>444954</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>34700</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="49" name="正方形/長方形 48"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="1126332" y="6948149"/>
+          <a:ext cx="263978" cy="1094695"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>237446</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>140836</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>651784</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>159885</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="50" name="正方形/長方形 49"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="8817091" y="1439977"/>
+          <a:ext cx="263978" cy="1094695"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>76881</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>122464</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>326571</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>121785</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="51" name="正方形/長方形 50"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="7754030" y="1344387"/>
+          <a:ext cx="1223964" cy="249690"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>530678</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>102054</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>469446</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>197304</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="52" name="楕円 51"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8694964" y="1081768"/>
+          <a:ext cx="619125" cy="585107"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
           <a:schemeClr val="accent4"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>405494</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>168729</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>338818</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="53" name="楕円 52"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2446565" y="2373086"/>
+          <a:ext cx="613682" cy="585107"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
         </a:solidFill>
       </xdr:spPr>
       <xdr:style>
@@ -3928,10 +4703,10 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B21:F26"/>
+  <dimension ref="B21:H30"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B21" t="s">
         <v>16</v>
       </c>
@@ -3941,8 +4716,11 @@
       <c r="F21" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="H21" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B26" t="s">
         <v>83</v>
       </c>
@@ -3951,6 +4729,11 @@
       </c>
       <c r="F26" t="s">
         <v>84</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B30" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" activeTab="7"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="ゲームの大まかな動き" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="ステータス一覧" sheetId="7" r:id="rId6"/>
     <sheet name="ステージ" sheetId="4" r:id="rId7"/>
     <sheet name="Stage1" sheetId="8" r:id="rId8"/>
+    <sheet name="menu" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -2255,8 +2256,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3457575" y="6248399"/>
-          <a:ext cx="1600200" cy="847725"/>
+          <a:off x="3430361" y="6425292"/>
+          <a:ext cx="1589314" cy="868136"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3842,6 +3843,715 @@
         </a:prstGeom>
         <a:solidFill>
           <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>314324</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="正方形/長方形 1"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1000124" y="1009650"/>
+          <a:ext cx="6000751" cy="2171700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="楕円 2"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1085850" y="1895475"/>
+          <a:ext cx="333375" cy="371475"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="楕円 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1571625" y="2638425"/>
+          <a:ext cx="333375" cy="371475"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>666750</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>310924</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>36739</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="正方形/長方形 4"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2038350" y="2457450"/>
+          <a:ext cx="329974" cy="1151164"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>358549</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>84364</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="正方形/長方形 5"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2085975" y="600075"/>
+          <a:ext cx="329974" cy="1151164"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="楕円 6"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2495550" y="1123950"/>
+          <a:ext cx="333375" cy="371475"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>219075</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>552450</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="楕円 7"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2962275" y="2600325"/>
+          <a:ext cx="333375" cy="371475"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>514350</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>219075</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="楕円 8"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3609975" y="1038225"/>
+          <a:ext cx="333375" cy="371475"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="楕円 9"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4076700" y="2638425"/>
+          <a:ext cx="333375" cy="371475"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>349024</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>17689</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="正方形/長方形 10"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4819650" y="2438400"/>
+          <a:ext cx="329974" cy="1151164"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>396649</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>65314</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="正方形/長方形 11"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4867275" y="581025"/>
+          <a:ext cx="329974" cy="1151164"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>638175</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="楕円 12"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6477000" y="1905000"/>
+          <a:ext cx="333375" cy="371475"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4"/>
         </a:solidFill>
       </xdr:spPr>
       <xdr:style>
@@ -4741,4 +5451,15 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -20,7 +20,8 @@
     <sheet name="ステータス一覧" sheetId="7" r:id="rId6"/>
     <sheet name="ステージ" sheetId="4" r:id="rId7"/>
     <sheet name="Stage1" sheetId="8" r:id="rId8"/>
-    <sheet name="menu" sheetId="9" r:id="rId9"/>
+    <sheet name="Stage2" sheetId="11" r:id="rId9"/>
+    <sheet name="menu" sheetId="9" r:id="rId10"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -3879,6 +3880,2636 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>145596</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="正方形/長方形 1"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1447800" y="3162300"/>
+          <a:ext cx="3943350" cy="1269546"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>552449</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>114299</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>352424</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>21770</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="正方形/長方形 2"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3295649" y="2257424"/>
+          <a:ext cx="1171575" cy="859971"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>619125</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>78921</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="正方形/長方形 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1476375" y="952500"/>
+          <a:ext cx="3943350" cy="1269546"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>428625</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>152401</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="正方形/長方形 4"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6600825" y="1104901"/>
+          <a:ext cx="3943350" cy="1114424"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>666750</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="右矢印 5"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="10800000">
+          <a:off x="2038350" y="2466975"/>
+          <a:ext cx="1200150" cy="457200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>676274</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>70086</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="正方形/長方形 6"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="3279657" y="2397243"/>
+          <a:ext cx="298686" cy="4095749"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>66676</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>47624</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>127237</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="正方形/長方形 7"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="3336807" y="-1117481"/>
+          <a:ext cx="298686" cy="4095749"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>276225</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>210909</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="正方形/長方形 8"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1390650" y="3143250"/>
+          <a:ext cx="257175" cy="1353909"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>514350</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>182334</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="正方形/長方形 9"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5314950" y="3114675"/>
+          <a:ext cx="257175" cy="1353909"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>447675</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="正方形/長方形 10"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4305300" y="2257425"/>
+          <a:ext cx="257175" cy="904875"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="正方形/長方形 11"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3162300" y="2238375"/>
+          <a:ext cx="257175" cy="904875"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>163284</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="正方形/長方形 12"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5276850" y="952500"/>
+          <a:ext cx="257175" cy="1353909"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>581025</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>172809</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="正方形/長方形 13"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1266825" y="962025"/>
+          <a:ext cx="257175" cy="1353909"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>276225</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>118382</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="楕円 14"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1647825" y="1200150"/>
+          <a:ext cx="619125" cy="585107"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent6"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>428625</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>156482</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="楕円 15"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1866900" y="3619500"/>
+          <a:ext cx="619125" cy="585107"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>657225</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>194582</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="楕円 16"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4152900" y="3419475"/>
+          <a:ext cx="619125" cy="585107"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>276225</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>13607</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="楕円 17"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3086100" y="1333500"/>
+          <a:ext cx="619125" cy="585107"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>80282</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="楕円 18"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8220075" y="1400175"/>
+          <a:ext cx="619125" cy="585107"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>152401</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="正方形/長方形 20"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6629400" y="4200526"/>
+          <a:ext cx="3943350" cy="1114424"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>38101</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="正方形/長方形 21"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6610350" y="2657476"/>
+          <a:ext cx="3943350" cy="1114424"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>657225</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>114301</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>223158</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="楕円 23"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6829425" y="2971801"/>
+          <a:ext cx="619125" cy="585107"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent6"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>114301</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>223158</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="25" name="楕円 24"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8296275" y="2971801"/>
+          <a:ext cx="619125" cy="585107"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent6"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>657225</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>108858</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="26" name="楕円 25"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9639300" y="4524376"/>
+          <a:ext cx="619125" cy="585107"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent6"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>95251</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>204108</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="27" name="楕円 26"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9744075" y="2952751"/>
+          <a:ext cx="619125" cy="585107"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent6"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>219076</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>89808</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="28" name="楕円 27"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6886575" y="4505326"/>
+          <a:ext cx="619125" cy="585107"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent6"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>666750</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>219076</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>89808</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="29" name="楕円 28"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8210550" y="4505326"/>
+          <a:ext cx="619125" cy="585107"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent6"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>209551</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="30" name="正方形/長方形 29"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6648450" y="5924551"/>
+          <a:ext cx="3943350" cy="1114424"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>61232</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="31" name="楕円 30"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9763125" y="6143625"/>
+          <a:ext cx="619125" cy="585107"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>485777</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>161926</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>466726</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>222487</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="33" name="正方形/長方形 32"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="8556509" y="-784106"/>
+          <a:ext cx="298686" cy="4095749"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>400053</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>142877</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>381002</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>203438</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="34" name="正方形/長方形 33"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="8470785" y="149345"/>
+          <a:ext cx="298686" cy="4095749"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>371478</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>114303</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>352427</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>174864</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="36" name="正方形/長方形 35"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="8442210" y="597021"/>
+          <a:ext cx="298686" cy="4095749"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>361953</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>85729</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>342902</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>146290</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="37" name="正方形/長方形 36"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="8432685" y="1759072"/>
+          <a:ext cx="298686" cy="4095749"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>476253</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>76205</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>457202</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>136766</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="38" name="正方形/長方形 37"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="8546985" y="2225798"/>
+          <a:ext cx="298686" cy="4095749"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>447678</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>171456</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>428627</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>232017</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="39" name="正方形/長方形 38"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="8518410" y="3273549"/>
+          <a:ext cx="298686" cy="4095749"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>409578</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>38107</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>390527</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>98668</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="40" name="正方形/長方形 39"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="8480310" y="3854575"/>
+          <a:ext cx="298686" cy="4095749"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>400053</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>190508</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>381002</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>12944</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="41" name="正方形/長方形 40"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="8470785" y="4959476"/>
+          <a:ext cx="298686" cy="4095749"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>39459</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="42" name="正方形/長方形 41"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6457950" y="1066800"/>
+          <a:ext cx="257175" cy="1353909"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>276225</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>220434</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="43" name="正方形/長方形 42"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10563225" y="1009650"/>
+          <a:ext cx="257175" cy="1353909"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>361950</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>619125</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>29934</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="44" name="正方形/長方形 43"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6534150" y="2486025"/>
+          <a:ext cx="257175" cy="1353909"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>514350</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>106134</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="45" name="正方形/長方形 44"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10544175" y="2562225"/>
+          <a:ext cx="257175" cy="1353909"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>581025</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>191859</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="46" name="正方形/長方形 45"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6496050" y="4076700"/>
+          <a:ext cx="257175" cy="1353909"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>182334</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="47" name="正方形/長方形 46"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10525125" y="4067175"/>
+          <a:ext cx="257175" cy="1353909"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>352425</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>220434</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="48" name="正方形/長方形 47"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6524625" y="5772150"/>
+          <a:ext cx="257175" cy="1353909"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>229959</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="49" name="正方形/長方形 48"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10572750" y="5781675"/>
+          <a:ext cx="257175" cy="1353909"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>314324</xdr:colOff>
       <xdr:row>4</xdr:row>
@@ -4891,6 +7522,17 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D29"/>

--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="95">
   <si>
     <t>ゲームの動き</t>
     <rPh sb="4" eb="5">
@@ -995,6 +995,70 @@
     </rPh>
     <rPh sb="3" eb="4">
       <t>カベ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>問題１</t>
+    <rPh sb="0" eb="2">
+      <t>モンダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Stage2にある木は、何本？</t>
+    <rPh sb="9" eb="10">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ナニ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ホン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>左から</t>
+    <rPh sb="0" eb="1">
+      <t>ヒダリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>問題２</t>
+    <rPh sb="0" eb="2">
+      <t>モンダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Stage2にある動く岩の数は？</t>
+    <rPh sb="9" eb="10">
+      <t>ウゴ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>イワ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>カズ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>問題３</t>
+    <rPh sb="0" eb="2">
+      <t>モンダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Stage2にいる敵の数は？</t>
+    <rPh sb="9" eb="10">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>カズ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -8097,9 +8161,78 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="R6:T19"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <sheetData/>
+  <sheetData>
+    <row r="6" spans="18:20" x14ac:dyDescent="0.4">
+      <c r="R6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="7" spans="18:20" x14ac:dyDescent="0.4">
+      <c r="R7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="8" spans="18:20" x14ac:dyDescent="0.4">
+      <c r="R8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" spans="18:20" x14ac:dyDescent="0.4">
+      <c r="R9">
+        <v>1</v>
+      </c>
+      <c r="S9">
+        <v>10</v>
+      </c>
+      <c r="T9">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="18:20" x14ac:dyDescent="0.4">
+      <c r="R11" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="12" spans="18:20" x14ac:dyDescent="0.4">
+      <c r="R12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="14" spans="18:20" x14ac:dyDescent="0.4">
+      <c r="R14">
+        <v>3</v>
+      </c>
+      <c r="S14">
+        <v>2</v>
+      </c>
+      <c r="T14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="18:20" x14ac:dyDescent="0.4">
+      <c r="R16" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="17" spans="18:20" x14ac:dyDescent="0.4">
+      <c r="R17" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="19" spans="18:20" x14ac:dyDescent="0.4">
+      <c r="R19">
+        <v>3</v>
+      </c>
+      <c r="S19">
+        <v>5</v>
+      </c>
+      <c r="T19">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" activeTab="8"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="ゲームの大まかな動き" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,8 @@
     <sheet name="ステージ" sheetId="4" r:id="rId7"/>
     <sheet name="Stage1" sheetId="8" r:id="rId8"/>
     <sheet name="Stage2" sheetId="11" r:id="rId9"/>
-    <sheet name="menu" sheetId="9" r:id="rId10"/>
+    <sheet name="Stage3" sheetId="12" r:id="rId10"/>
+    <sheet name="menu" sheetId="9" r:id="rId11"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -6575,6 +6576,4047 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>561975</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>174171</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="正方形/長方形 2"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="727982" y="575582"/>
+          <a:ext cx="3916136" cy="3272518"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>29936</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>130629</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>544286</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>225879</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="正方形/長方形 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="710293" y="6988629"/>
+          <a:ext cx="3916136" cy="3279321"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>316454</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>167422</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>143349</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>227859</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="正方形/長方形 4"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3718240" y="5800779"/>
+          <a:ext cx="507252" cy="1774937"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>542418</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>1272</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>276717</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>232098</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="正方形/長方形 5"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="17751263">
+          <a:off x="2552940" y="4494964"/>
+          <a:ext cx="475755" cy="1775371"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>348961</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>236332</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>140846</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>28062</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="正方形/長方形 6"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="1883483">
+          <a:off x="1709675" y="2685618"/>
+          <a:ext cx="472242" cy="2241015"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>13606</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>560614</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="正方形/長方形 7"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3415392" y="5334000"/>
+          <a:ext cx="1227365" cy="1167493"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>274863</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>84364</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>141514</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>27214</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="正方形/長方形 8"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="955220" y="4493078"/>
+          <a:ext cx="1227365" cy="1167493"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>417739</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>6804</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>251732</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="正方形/長方形 9"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6540953" y="496661"/>
+          <a:ext cx="3916136" cy="3272518"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>424543</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>166007</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>291193</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>108858</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="正方形/長方形 10"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6547757" y="3839936"/>
+          <a:ext cx="1227365" cy="1167493"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>434068</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>172811</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>268061</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>16329</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="正方形/長方形 11"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6557282" y="5071382"/>
+          <a:ext cx="3916136" cy="3272518"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>355146</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>107496</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>189140</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>195943</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="正方形/長方形 12"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12601575" y="2556782"/>
+          <a:ext cx="3916136" cy="3272518"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>332014</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>223157</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>198665</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>166007</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="正方形/長方形 13"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13939157" y="1447800"/>
+          <a:ext cx="1227365" cy="1167493"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>361949</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>89807</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>32657</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="正方形/長方形 14"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13969092" y="5723164"/>
+          <a:ext cx="1227365" cy="1167493"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>666749</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>27214</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>605517</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>122464</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="楕円 15"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14273892" y="1741714"/>
+          <a:ext cx="619125" cy="585107"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>421821</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>176894</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>360589</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>27215</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="楕円 16"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3143250" y="7524751"/>
+          <a:ext cx="619125" cy="585107"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>206829</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>111580</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>145597</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>206830</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="楕円 17"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3608615" y="9173937"/>
+          <a:ext cx="619125" cy="585107"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>372837</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>114301</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>311604</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>209551</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="楕円 18"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2413908" y="849087"/>
+          <a:ext cx="619125" cy="585107"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>321129</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>212273</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>259897</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>62594</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="楕円 19"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1001486" y="2416630"/>
+          <a:ext cx="619125" cy="585107"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>644980</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>127908</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>583748</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>223158</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="楕円 20"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1325337" y="7475765"/>
+          <a:ext cx="619125" cy="585107"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>130630</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>62593</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>69398</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>157843</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="楕円 21"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3532416" y="3001736"/>
+          <a:ext cx="619125" cy="585107"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>157844</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>8166</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>96611</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>103416</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name="楕円 22"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6961415" y="987880"/>
+          <a:ext cx="619125" cy="585107"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>636814</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>65315</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>575582</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>160565</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="楕円 23"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8120743" y="3004458"/>
+          <a:ext cx="619125" cy="585107"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>81644</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>224518</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>176894</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="25" name="楕円 24"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9130393" y="5470073"/>
+          <a:ext cx="619125" cy="585107"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>274865</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>138795</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>213632</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>234045</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="26" name="楕円 25"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7078436" y="7486652"/>
+          <a:ext cx="619125" cy="585107"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>114301</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>182339</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>53069</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>32660</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="27" name="楕円 26"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8958944" y="1896839"/>
+          <a:ext cx="619125" cy="585107"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>185057</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>157845</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>8166</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="28" name="楕円 27"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13111843" y="5056416"/>
+          <a:ext cx="619125" cy="585107"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>160564</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>24494</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>99332</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>119744</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="29" name="楕円 28"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13087350" y="4188280"/>
+          <a:ext cx="619125" cy="585107"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>149678</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>163288</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>88446</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>13609</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="30" name="楕円 29"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13076464" y="3347359"/>
+          <a:ext cx="619125" cy="585107"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>315685</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>84366</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>254453</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>179615</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="31" name="楕円 30"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15283542" y="3268437"/>
+          <a:ext cx="619125" cy="585107"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>372835</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>236766</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>311603</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>87087</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="32" name="楕円 31"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15340692" y="4155623"/>
+          <a:ext cx="619125" cy="585107"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>334735</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>198666</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>273503</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>48987</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="33" name="楕円 32"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15302592" y="5097237"/>
+          <a:ext cx="619125" cy="585107"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>625929</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>68038</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>272143</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>121792</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="34" name="正方形/長方形 33"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="2000587" y="5551380"/>
+          <a:ext cx="298683" cy="3048000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>206831</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>68039</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>653143</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>110909</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="35" name="正方形/長方形 34"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="4368230" y="6846783"/>
+          <a:ext cx="287799" cy="446312"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2721</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>81646</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>612320</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>124516</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="36" name="正方形/長方形 35"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="2544871" y="8261924"/>
+          <a:ext cx="287799" cy="4011385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>503798</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>18716</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>217714</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>54095</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="37" name="正方形/長方形 36"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4585941" y="6876716"/>
+          <a:ext cx="394273" cy="3954236"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>356841</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>35045</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>70757</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>70424</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="38" name="正方形/長方形 37"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="356841" y="6893045"/>
+          <a:ext cx="394273" cy="3954236"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>495634</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>24159</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>59538</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="39" name="正方形/長方形 38"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="495634" y="24159"/>
+          <a:ext cx="394273" cy="3954236"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>362284</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>81309</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>116688</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="40" name="正方形/長方形 39"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4444427" y="81309"/>
+          <a:ext cx="394273" cy="3954236"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>206830</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>628649</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>4772</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="41" name="正方形/長方形 40"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="2561200" y="-1410034"/>
+          <a:ext cx="287799" cy="4011385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>16329</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>43545</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>97300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="42" name="正方形/長方形 41"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="3432058" y="2342816"/>
+          <a:ext cx="298683" cy="3048000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>195945</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>70763</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>190499</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>81646</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="43" name="正方形/長方形 42"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="1085852" y="3535142"/>
+          <a:ext cx="255811" cy="674911"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>386443</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>166010</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>315685</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>208881</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="44" name="正方形/長方形 43"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="8371450" y="6386860"/>
+          <a:ext cx="287799" cy="4011385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>402772</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>155124</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>332014</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>197995</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="45" name="正方形/長方形 44"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="8387779" y="-1461740"/>
+          <a:ext cx="287799" cy="4011385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>133684</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>527957</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>35379</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="46" name="正方形/長方形 45"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6256898" y="0"/>
+          <a:ext cx="394273" cy="3954236"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>81977</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>35379</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="47" name="正方形/長方形 46"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10287334" y="0"/>
+          <a:ext cx="394273" cy="3954236"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>43876</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>171117</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>438149</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>206495</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="48" name="正方形/長方形 47"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10249233" y="5069688"/>
+          <a:ext cx="394273" cy="3954236"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>114633</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>105803</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>508906</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>141181</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="49" name="正方形/長方形 48"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6237847" y="5004374"/>
+          <a:ext cx="394273" cy="3954236"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>68369</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>138792</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>462642</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>174171</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="50" name="正方形/長方形 49"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12314798" y="2098221"/>
+          <a:ext cx="394273" cy="3954236"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>16663</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>127906</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>410936</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>163285</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="51" name="正方形/長方形 50"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16345234" y="2087335"/>
+          <a:ext cx="394273" cy="3954236"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>59873</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>163289</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>557893</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>4773</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="52" name="正方形/長方形 51"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="15791426" y="1603950"/>
+          <a:ext cx="331341" cy="1858734"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>538845</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>125190</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>356507</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>211602</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="53" name="正方形/長方形 52"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="12868612" y="1565851"/>
+          <a:ext cx="331341" cy="1858734"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>555174</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>168734</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>372836</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>10218</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="54" name="正方形/長方形 53"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="12884941" y="4793467"/>
+          <a:ext cx="331341" cy="1858734"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>176895</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>239492</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>674915</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>80976</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="55" name="正方形/長方形 54"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="15908448" y="4864225"/>
+          <a:ext cx="331341" cy="1858734"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>166009</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>10893</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>664029</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>97305</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="56" name="正方形/長方形 55"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="14536848" y="6105197"/>
+          <a:ext cx="331341" cy="1858734"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>46266</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>8</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>544286</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>86421</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="57" name="正方形/長方形 56"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="14417105" y="460955"/>
+          <a:ext cx="331341" cy="1858734"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>132327</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>218748</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>463668</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>118053</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="58" name="正方形/長方形 57"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15100184" y="708605"/>
+          <a:ext cx="331341" cy="1858734"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>39798</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>17362</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>371139</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>161596</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="59" name="正方形/長方形 58"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13646941" y="752148"/>
+          <a:ext cx="331341" cy="1858734"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>69733</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>101727</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>401074</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>1032</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="60" name="正方形/長方形 59"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13676876" y="5735084"/>
+          <a:ext cx="331341" cy="1858734"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>154098</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>145270</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>485439</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>44575</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="61" name="正方形/長方形 60"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15121955" y="5778627"/>
+          <a:ext cx="331341" cy="1858734"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>340178</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>54429</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>278946</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>149679</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="62" name="楕円 61"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1020535" y="9361715"/>
+          <a:ext cx="619125" cy="585107"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>125185</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>193222</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>63953</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>43543</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="65" name="楕円 64"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8969828" y="7541079"/>
+          <a:ext cx="619125" cy="585107"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>617763</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>195943</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>556531</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>46265</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="66" name="楕円 65"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14224906" y="6074229"/>
+          <a:ext cx="619125" cy="585107"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>449036</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>163286</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>387804</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>13608</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="67" name="楕円 66"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1129393" y="898072"/>
+          <a:ext cx="619125" cy="585107"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent6"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>465365</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>166007</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>404133</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>16329</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="68" name="楕円 67"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9310008" y="900793"/>
+          <a:ext cx="619125" cy="585107"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent6"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>477949</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>40821</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>81644</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>177925</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="71" name="正方形/長方形 70"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4560092" y="5184321"/>
+          <a:ext cx="284052" cy="1361747"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>31635</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>193221</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>315687</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>85397</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="72" name="正方形/長方形 71"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="711992" y="4357007"/>
+          <a:ext cx="284052" cy="1361747"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>200357</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>206834</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>201390</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>77228</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="73" name="正方形/長方形 72"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="1381462" y="4849586"/>
+          <a:ext cx="360251" cy="1361747"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>12578</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>32663</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>13611</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>147985</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="74" name="正方形/長方形 73"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="3915112" y="4675415"/>
+          <a:ext cx="360251" cy="1361747"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>314324</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
@@ -7587,6 +11629,17 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>

--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="96">
   <si>
     <t>ゲームの動き</t>
     <rPh sb="4" eb="5">
@@ -1060,6 +1060,13 @@
     </rPh>
     <rPh sb="11" eb="12">
       <t>カズ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジャンプ台</t>
+    <rPh sb="4" eb="5">
+      <t>ダイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -7032,15 +7039,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>424543</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>166007</xdr:rowOff>
+      <xdr:colOff>506186</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>206828</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>291193</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>108858</xdr:rowOff>
+      <xdr:colOff>372836</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>149678</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -7049,7 +7056,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6547757" y="3839936"/>
+          <a:off x="6629400" y="4370614"/>
           <a:ext cx="1227365" cy="1167493"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -11630,9 +11637,15 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="M20"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <sheetData/>
+  <sheetData>
+    <row r="20" spans="13:13" x14ac:dyDescent="0.4">
+      <c r="M20" t="s">
+        <v>95</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" activeTab="9"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="ゲームの大まかな動き" sheetId="1" r:id="rId1"/>
@@ -7038,16 +7038,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>506186</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>206828</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>57151</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>220436</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>372836</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>149678</xdr:rowOff>
+      <xdr:colOff>604158</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>163286</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -7056,7 +7056,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6629400" y="4370614"/>
+          <a:off x="6860722" y="4139293"/>
           <a:ext cx="1227365" cy="1167493"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -7380,71 +7380,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>421821</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>176894</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>360589</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>27215</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="17" name="楕円 16"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3143250" y="7524751"/>
-          <a:ext cx="619125" cy="585107"/>
-        </a:xfrm>
-        <a:prstGeom prst="ellipse">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="FF0000"/>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>206829</xdr:colOff>
+      <xdr:colOff>70757</xdr:colOff>
       <xdr:row>37</xdr:row>
       <xdr:rowOff>111580</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>145597</xdr:colOff>
+      <xdr:colOff>9525</xdr:colOff>
       <xdr:row>39</xdr:row>
       <xdr:rowOff>206830</xdr:rowOff>
     </xdr:to>
@@ -7455,7 +7398,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3608615" y="9173937"/>
+          <a:off x="3472543" y="9173937"/>
           <a:ext cx="619125" cy="585107"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
@@ -7495,15 +7438,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>372837</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>114301</xdr:rowOff>
+      <xdr:colOff>209552</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>46266</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>311604</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>209551</xdr:rowOff>
+      <xdr:colOff>148319</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>141516</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -7512,7 +7455,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2413908" y="849087"/>
+          <a:off x="2250623" y="1025980"/>
           <a:ext cx="619125" cy="585107"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
@@ -7609,15 +7552,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>644980</xdr:colOff>
+      <xdr:colOff>468087</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>127908</xdr:rowOff>
+      <xdr:rowOff>46265</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>583748</xdr:colOff>
+      <xdr:colOff>406855</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>223158</xdr:rowOff>
+      <xdr:rowOff>141515</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -7626,7 +7569,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1325337" y="7475765"/>
+          <a:off x="1148444" y="7394122"/>
           <a:ext cx="619125" cy="585107"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
@@ -7722,25 +7665,82 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>212272</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>117023</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>151040</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>212273</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name="楕円 22"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7696201" y="851809"/>
+          <a:ext cx="619125" cy="585107"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>157844</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>8166</xdr:rowOff>
+      <xdr:colOff>446314</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>201387</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>96611</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>103416</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="23" name="楕円 22"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6961415" y="987880"/>
+      <xdr:colOff>385081</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>51708</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="楕円 23"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7249885" y="2405744"/>
           <a:ext cx="619125" cy="585107"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
@@ -7779,25 +7779,82 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>312964</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>176894</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>251732</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>27216</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="25" name="楕円 24"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9157607" y="7279823"/>
+          <a:ext cx="619125" cy="585107"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>84365</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>636814</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>65315</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>575582</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>160565</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="24" name="楕円 23"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8120743" y="3004458"/>
+      <xdr:colOff>186417</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>179615</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="26" name="楕円 25"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7051221" y="5472794"/>
           <a:ext cx="619125" cy="585107"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
@@ -7837,129 +7894,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>285750</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>81644</xdr:rowOff>
+      <xdr:colOff>250372</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>127911</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>224518</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>176894</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="25" name="楕円 24"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9130393" y="5470073"/>
-          <a:ext cx="619125" cy="585107"/>
-        </a:xfrm>
-        <a:prstGeom prst="ellipse">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="FF0000"/>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>274865</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>138795</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>213632</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>234045</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="26" name="楕円 25"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7078436" y="7486652"/>
-          <a:ext cx="619125" cy="585107"/>
-        </a:xfrm>
-        <a:prstGeom prst="ellipse">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="FF0000"/>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>114301</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>182339</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>53069</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>32660</xdr:rowOff>
+      <xdr:colOff>189140</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>223161</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -7968,7 +7911,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8958944" y="1896839"/>
+          <a:off x="9095015" y="1842411"/>
           <a:ext cx="619125" cy="585107"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
@@ -10142,16 +10085,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>125185</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>669470</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>193222</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>63953</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>43543</xdr:rowOff>
+      <xdr:rowOff>125186</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>608238</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>220436</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -10160,7 +10103,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8969828" y="7541079"/>
+          <a:off x="6792684" y="7473043"/>
           <a:ext cx="619125" cy="585107"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
@@ -10256,16 +10199,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>449036</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>27214</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>163286</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>387804</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>13608</xdr:rowOff>
+      <xdr:rowOff>136072</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>646339</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>231322</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -10274,7 +10217,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1129393" y="898072"/>
+          <a:off x="3429000" y="870858"/>
           <a:ext cx="619125" cy="585107"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">

--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="ゲームの大まかな動き" sheetId="1" r:id="rId1"/>
@@ -1535,6 +1535,1481 @@
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="正方形/長方形 1"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2771775" y="752475"/>
+          <a:ext cx="7905750" cy="4124325"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="角丸四角形 2"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3009900" y="2971800"/>
+          <a:ext cx="1133475" cy="609600"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>装備</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="角丸四角形 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3009900" y="4000500"/>
+          <a:ext cx="1133475" cy="609600"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>ステータス</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="角丸四角形 4"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3048000" y="1905000"/>
+          <a:ext cx="1133475" cy="609600"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>回復薬</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>485775</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="角丸四角形 5"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4895850" y="1724025"/>
+          <a:ext cx="1076325" cy="781050"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="角丸四角形 6"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6610350" y="1771650"/>
+          <a:ext cx="1076325" cy="781050"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="角丸四角形 7"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8486775" y="1790700"/>
+          <a:ext cx="1076325" cy="781050"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="角丸四角形 8"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4905375" y="2809875"/>
+          <a:ext cx="1076325" cy="781050"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="角丸四角形 9"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6667500" y="2828925"/>
+          <a:ext cx="1076325" cy="781050"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="角丸四角形 10"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8553450" y="2847975"/>
+          <a:ext cx="1076325" cy="781050"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="角丸四角形 11"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4943475" y="3952875"/>
+          <a:ext cx="1076325" cy="781050"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>504825</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="角丸四角形 12"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6677025" y="3971925"/>
+          <a:ext cx="1076325" cy="781050"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>333375</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="角丸四角形 13"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8562975" y="3981450"/>
+          <a:ext cx="1076325" cy="781050"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>19051</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>209551</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="角丸四角形 14"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8248651" y="847725"/>
+          <a:ext cx="2247900" cy="542925"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>所持金</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>238126</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>390526</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>219075</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="角丸四角形 15"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2981326" y="857250"/>
+          <a:ext cx="838200" cy="552450"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>戻る</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>666750</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>638175</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="角丸四角形 16"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4095750" y="904875"/>
+          <a:ext cx="2028825" cy="581025"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>SHOP</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>314325</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>53068</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>129269</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="正方形/長方形 17"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11880396" y="787854"/>
+          <a:ext cx="7845879" cy="4239986"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>519793</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>189139</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>281667</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>84364</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="角丸四角形 18"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12085864" y="3128282"/>
+          <a:ext cx="1122589" cy="630011"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>装備</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>519793</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>20410</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>281667</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>160564</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="角丸四角形 19"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12085864" y="4184196"/>
+          <a:ext cx="1122589" cy="630011"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>ステータス</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>557893</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>74839</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>319767</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>208189</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="角丸四角形 20"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12123964" y="2034268"/>
+          <a:ext cx="1122589" cy="623207"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>回復薬</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>272143</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>208189</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>462643</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>29936</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="角丸四角形 21"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17281072" y="942975"/>
+          <a:ext cx="2231571" cy="556532"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>所持金</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>491219</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>217714</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>643618</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>48986</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name="角丸四角形 22"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12057290" y="952500"/>
+          <a:ext cx="832757" cy="566057"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>戻る</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>239485</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>20411</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>210910</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>131989</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="角丸四角形 23"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13166271" y="1000125"/>
+          <a:ext cx="2012496" cy="601435"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>SHOP</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>14967</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>68035</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>405492</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>214993</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="25" name="角丸四角形 24"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13622110" y="2027464"/>
+          <a:ext cx="1070882" cy="391886"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>hp</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>24492</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>204862</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>415017</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>110218</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="26" name="角丸四角形 25"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13631635" y="3144005"/>
+          <a:ext cx="1070882" cy="395213"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>power</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>62592</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>153760</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>453117</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>55789</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="27" name="角丸四角形 26"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13669735" y="4317546"/>
+          <a:ext cx="1070882" cy="391886"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>defence</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
@@ -1593,7 +3068,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -3948,7 +5423,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -6578,7 +8053,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -10562,7 +12037,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -11980,6 +13455,7 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="110">
   <si>
     <t>ゲームの動き</t>
     <rPh sb="4" eb="5">
@@ -1067,6 +1067,113 @@
     <t>ジャンプ台</t>
     <rPh sb="4" eb="5">
       <t>ダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステータス上げるのに</t>
+    <rPh sb="5" eb="6">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>と５０ずつ値上げする</t>
+    <rPh sb="5" eb="7">
+      <t>ネア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スケルトンが落とす金額</t>
+    <rPh sb="6" eb="7">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>キンガク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゴーレムが落とす金額</t>
+    <rPh sb="5" eb="6">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>キンガク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>回復薬</t>
+    <rPh sb="0" eb="3">
+      <t>カイフクヤク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>名前</t>
+    <rPh sb="0" eb="2">
+      <t>ナマエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>値段</t>
+    <rPh sb="0" eb="2">
+      <t>ネダン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>所持制限</t>
+    <rPh sb="0" eb="4">
+      <t>ショジセイゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>聖水</t>
+    <rPh sb="0" eb="2">
+      <t>セイスイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>秘伝の薬</t>
+    <rPh sb="0" eb="2">
+      <t>ヒデン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>クスリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>効果</t>
+    <rPh sb="0" eb="2">
+      <t>コウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>１００回復</t>
+    <rPh sb="3" eb="5">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>１０回復</t>
+    <rPh sb="2" eb="4">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>３０回復</t>
+    <rPh sb="2" eb="4">
+      <t>カイフク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -13429,7 +13536,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -13452,10 +13559,132 @@
         <v>67</v>
       </c>
     </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A10">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A11">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A12">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A13">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A14">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A19">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A21">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A27" t="s">
+        <v>101</v>
+      </c>
+      <c r="B27" t="s">
+        <v>102</v>
+      </c>
+      <c r="C27" t="s">
+        <v>103</v>
+      </c>
+      <c r="D27" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A28" t="s">
+        <v>100</v>
+      </c>
+      <c r="B28">
+        <v>100</v>
+      </c>
+      <c r="C28">
+        <v>10</v>
+      </c>
+      <c r="D28" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A29" t="s">
+        <v>104</v>
+      </c>
+      <c r="B29">
+        <v>300</v>
+      </c>
+      <c r="C29">
+        <v>5</v>
+      </c>
+      <c r="D29" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A30" t="s">
+        <v>105</v>
+      </c>
+      <c r="B30">
+        <v>500</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30" t="s">
+        <v>107</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="ゲームの大まかな動き" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="110">
   <si>
     <t>ゲームの動き</t>
     <rPh sb="4" eb="5">
@@ -13468,11 +13468,6 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
-        <v>43</v>
-      </c>
-    </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>58</v>

--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="111">
   <si>
     <t>ゲームの動き</t>
     <rPh sb="4" eb="5">
@@ -1174,6 +1174,16 @@
     <t>３０回復</t>
     <rPh sb="2" eb="4">
       <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>２，ボスの周囲攻撃</t>
+    <rPh sb="5" eb="7">
+      <t>シュウイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>コウゲキ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -13465,11 +13475,11 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>42</v>
+        <v>110</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
         <v>58</v>
       </c>
     </row>

--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" firstSheet="1" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="ゲームの大まかな動き" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="112">
   <si>
     <t>ゲームの動き</t>
     <rPh sb="4" eb="5">
@@ -1186,6 +1186,9 @@
       <t>コウゲキ</t>
     </rPh>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジャンプ台</t>
   </si>
 </sst>
 </file>
@@ -8576,13 +8579,13 @@
       <xdr:col>9</xdr:col>
       <xdr:colOff>417739</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>6804</xdr:rowOff>
+      <xdr:rowOff>102054</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>251732</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -8591,7 +8594,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6540953" y="496661"/>
+          <a:off x="6540953" y="591911"/>
           <a:ext cx="3916136" cy="3272518"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -8632,14 +8635,14 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>57151</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>220436</xdr:rowOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>70757</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>604158</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>163286</xdr:rowOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>13607</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -8648,7 +8651,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6860722" y="4139293"/>
+          <a:off x="6860722" y="4234543"/>
           <a:ext cx="1227365" cy="1167493"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -9260,13 +9263,13 @@
       <xdr:col>11</xdr:col>
       <xdr:colOff>212272</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>117023</xdr:rowOff>
+      <xdr:rowOff>212273</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>151040</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>212273</xdr:rowOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>62595</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -9275,7 +9278,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7696201" y="851809"/>
+          <a:off x="7696201" y="947059"/>
           <a:ext cx="619125" cy="585107"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
@@ -9316,14 +9319,14 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>446314</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>201387</xdr:rowOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>51708</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>385081</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>51708</xdr:rowOff>
+      <xdr:rowOff>146958</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -9332,7 +9335,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7249885" y="2405744"/>
+          <a:off x="7249885" y="2500994"/>
           <a:ext cx="619125" cy="585107"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
@@ -9488,13 +9491,13 @@
       <xdr:col>13</xdr:col>
       <xdr:colOff>250372</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>127911</xdr:rowOff>
+      <xdr:rowOff>223161</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>189140</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>223161</xdr:rowOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>73482</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -9503,7 +9506,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9095015" y="1842411"/>
+          <a:off x="9095015" y="1937661"/>
           <a:ext cx="619125" cy="585107"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
@@ -10568,14 +10571,14 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>402772</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>155124</xdr:rowOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>5446</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>332014</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>197995</xdr:rowOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>48316</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -10584,7 +10587,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm rot="5400000">
-          <a:off x="8387779" y="-1461740"/>
+          <a:off x="8387779" y="-1366490"/>
           <a:ext cx="287799" cy="4011385"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -10631,13 +10634,13 @@
       <xdr:col>9</xdr:col>
       <xdr:colOff>133684</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>527957</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>35379</xdr:rowOff>
+      <xdr:rowOff>130629</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -10646,7 +10649,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6256898" y="0"/>
+          <a:off x="6256898" y="95250"/>
           <a:ext cx="394273" cy="3954236"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -10693,13 +10696,13 @@
       <xdr:col>15</xdr:col>
       <xdr:colOff>81977</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>476250</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>35379</xdr:rowOff>
+      <xdr:rowOff>130629</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -10708,7 +10711,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10287334" y="0"/>
+          <a:off x="10287334" y="95250"/>
           <a:ext cx="394273" cy="3954236"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -11850,14 +11853,14 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>465365</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>166007</xdr:rowOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>16329</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>404133</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>16329</xdr:rowOff>
+      <xdr:rowOff>111579</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -11866,7 +11869,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9310008" y="900793"/>
+          <a:off x="9310008" y="996043"/>
           <a:ext cx="619125" cy="585107"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
@@ -12123,6 +12126,1319 @@
             <a:schemeClr val="tx1"/>
           </a:solidFill>
         </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>213194</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>16090</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>543810</xdr:colOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>165435</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="2" name="グループ化 1"/>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="893551" y="20835019"/>
+          <a:ext cx="4412759" cy="4802987"/>
+          <a:chOff x="688853" y="18307049"/>
+          <a:chExt cx="4405659" cy="4802989"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="70" name="正方形/長方形 69"/>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="2305050" y="18307049"/>
+            <a:ext cx="1227365" cy="1167493"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg2"/>
+          </a:solidFill>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="75" name="正方形/長方形 74"/>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="1008288" y="19147971"/>
+            <a:ext cx="3916136" cy="3282043"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg2"/>
+          </a:solidFill>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="78" name="楕円 77"/>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="3608613" y="21365937"/>
+            <a:ext cx="619125" cy="585107"/>
+          </a:xfrm>
+          <a:prstGeom prst="ellipse">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="79" name="楕円 78"/>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="1502227" y="19599729"/>
+            <a:ext cx="619125" cy="585107"/>
+          </a:xfrm>
+          <a:prstGeom prst="ellipse">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="84" name="正方形/長方形 83"/>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4700239" y="19155802"/>
+            <a:ext cx="394273" cy="3954236"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="85" name="正方形/長方形 84"/>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="688853" y="19090488"/>
+            <a:ext cx="394273" cy="3954236"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="86" name="楕円 85"/>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="1243690" y="21559157"/>
+            <a:ext cx="619125" cy="585107"/>
+          </a:xfrm>
+          <a:prstGeom prst="ellipse">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="accent5"/>
+          </a:solidFill>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>27546</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>220436</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>370112</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>10886</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="17" name="グループ化 16"/>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="707903" y="12711793"/>
+          <a:ext cx="4424709" cy="3954236"/>
+          <a:chOff x="707904" y="14222185"/>
+          <a:chExt cx="4424709" cy="3954236"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="69" name="正方形/長方形 68"/>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="991959" y="14718846"/>
+            <a:ext cx="3916136" cy="3272518"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg2"/>
+          </a:solidFill>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="76" name="楕円 75"/>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="2147207" y="15073994"/>
+            <a:ext cx="619125" cy="585107"/>
+          </a:xfrm>
+          <a:prstGeom prst="ellipse">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="77" name="楕円 76"/>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="1700891" y="16627929"/>
+            <a:ext cx="619125" cy="585107"/>
+          </a:xfrm>
+          <a:prstGeom prst="ellipse">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="80" name="楕円 79"/>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="3546021" y="16064596"/>
+            <a:ext cx="619125" cy="585107"/>
+          </a:xfrm>
+          <a:prstGeom prst="ellipse">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="81" name="正方形/長方形 80"/>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm rot="5400000">
+            <a:off x="2838785" y="12760445"/>
+            <a:ext cx="287799" cy="4011385"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="82" name="正方形/長方形 81"/>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="707904" y="14222185"/>
+            <a:ext cx="394273" cy="3954236"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="83" name="正方形/長方形 82"/>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4738340" y="14222185"/>
+            <a:ext cx="394273" cy="3954236"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="87" name="楕円 86"/>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="3761014" y="15122978"/>
+            <a:ext cx="619125" cy="585107"/>
+          </a:xfrm>
+          <a:prstGeom prst="ellipse">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="accent6"/>
+          </a:solidFill>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>164473</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>36017</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>204393</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>185360</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="88" name="正方形/長方形 87"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000">
+          <a:off x="3083218" y="17194316"/>
+          <a:ext cx="389539" cy="2102289"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>389283</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>185028</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>205558</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>226310</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="89" name="正方形/長方形 88"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2451653" y="18439898"/>
+          <a:ext cx="1878644" cy="1482455"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>208961</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>29256</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>536003</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>209194</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="90" name="正方形/長方形 89"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4333700" y="18043930"/>
+          <a:ext cx="327042" cy="900525"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>203518</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>151840</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>541446</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>223630</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="91" name="正方形/長方形 90"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4328257" y="19367492"/>
+          <a:ext cx="337928" cy="552181"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>69574</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>155212</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>389282</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>33131</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="92" name="正方形/長方形 91"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="757031" y="18890473"/>
+          <a:ext cx="1694621" cy="598506"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>414130</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>157370</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>64601</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>33130</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="93" name="正方形/長方形 92"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="414130" y="18892631"/>
+          <a:ext cx="337928" cy="596347"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>422163</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>140556</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>333213</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>153807</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="94" name="正方形/長方形 93"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="561562" y="17742505"/>
+          <a:ext cx="1694621" cy="598506"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>77856</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>140806</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>415784</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>160684</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="95" name="正方形/長方形 94"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="765313" y="17194697"/>
+          <a:ext cx="337928" cy="1701248"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>69572</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>36443</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>380999</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>99391</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="96" name="正方形/長方形 95"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="757029" y="19492291"/>
+          <a:ext cx="1686340" cy="303143"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>387129</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>99391</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>364435</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>134678</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="97" name="正方形/長方形 96"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1074586" y="16672891"/>
+          <a:ext cx="664762" cy="515678"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
@@ -13172,12 +14488,17 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="M20"/>
+  <dimension ref="D20:M71"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="20" spans="13:13" x14ac:dyDescent="0.4">
       <c r="M20" t="s">
         <v>95</v>
+      </c>
+    </row>
+    <row r="71" spans="4:4" x14ac:dyDescent="0.4">
+      <c r="D71" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
